--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130800748</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130800737</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130800759</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130800763</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130800732</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130800736</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130800755</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130800751</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130800767</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130800746</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130800747</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130800740</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130800741</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800615</v>
+        <v>130800639</v>
       </c>
       <c r="B15" t="n">
-        <v>57052</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,27 +2077,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488401</v>
+        <v>488441</v>
       </c>
       <c r="R15" t="n">
-        <v>6721155</v>
+        <v>6721177</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,6 +2160,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2178,50 +2179,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800769</v>
+        <v>130800750</v>
       </c>
       <c r="B16" t="n">
-        <v>5177</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488274</v>
+        <v>488188</v>
       </c>
       <c r="R16" t="n">
-        <v>6721118</v>
+        <v>6721096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800750</v>
+        <v>130800745</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,10 +2321,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488188</v>
+        <v>488254</v>
       </c>
       <c r="R17" t="n">
-        <v>6721096</v>
+        <v>6721190</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2356,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2366,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,45 +2393,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800745</v>
+        <v>130800769</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488254</v>
+        <v>488274</v>
       </c>
       <c r="R18" t="n">
-        <v>6721190</v>
+        <v>6721118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2468,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2478,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800639</v>
+        <v>130800615</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>57053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,27 +2516,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2544,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488441</v>
+        <v>488401</v>
       </c>
       <c r="R19" t="n">
-        <v>6721177</v>
+        <v>6721155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,7 +2599,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>130800752</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800624</v>
+        <v>130800734</v>
       </c>
       <c r="B22" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,39 +2847,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488277</v>
+        <v>488276</v>
       </c>
       <c r="R22" t="n">
-        <v>6721389</v>
+        <v>6721374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2921,7 +2916,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800734</v>
+        <v>130800624</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,34 +2954,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488276</v>
+        <v>488277</v>
       </c>
       <c r="R23" t="n">
-        <v>6721374</v>
+        <v>6721389</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800756</v>
+        <v>130800625</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,34 +3066,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488470</v>
+        <v>488400</v>
       </c>
       <c r="R24" t="n">
-        <v>6721165</v>
+        <v>6721188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3135,7 +3140,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,38 +3167,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800625</v>
+        <v>130800640</v>
       </c>
       <c r="B25" t="n">
-        <v>57859</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3202,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488400</v>
+        <v>488413</v>
       </c>
       <c r="R25" t="n">
-        <v>6721188</v>
+        <v>6721172</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,7 +3242,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3247,7 +3252,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,6 +3261,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3274,50 +3280,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800640</v>
+        <v>130800756</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488413</v>
+        <v>488470</v>
       </c>
       <c r="R26" t="n">
-        <v>6721172</v>
+        <v>6721165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,7 +3350,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3360,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3369,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>130800735</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>130800762</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800628</v>
+        <v>130800760</v>
       </c>
       <c r="B29" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,39 +3612,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488274</v>
+        <v>488321</v>
       </c>
       <c r="R29" t="n">
-        <v>6721118</v>
+        <v>6721317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3671,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3686,7 +3681,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800760</v>
+        <v>130800761</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3748,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488321</v>
+        <v>488353</v>
       </c>
       <c r="R30" t="n">
-        <v>6721317</v>
+        <v>6721338</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3793,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800761</v>
+        <v>130800628</v>
       </c>
       <c r="B31" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,34 +3826,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488353</v>
+        <v>488274</v>
       </c>
       <c r="R31" t="n">
-        <v>6721338</v>
+        <v>6721118</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,7 +3930,7 @@
         <v>130800757</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>130800742</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>130800749</v>
       </c>
       <c r="B34" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>130800758</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>130800743</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>130800754</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>130800765</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>130800739</v>
       </c>
       <c r="B40" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>130800605</v>
       </c>
       <c r="B41" t="n">
-        <v>90819</v>
+        <v>90820</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>130800647</v>
       </c>
       <c r="B42" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>130800753</v>
       </c>
       <c r="B43" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>130800738</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>130800744</v>
       </c>
       <c r="B45" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>130800731</v>
       </c>
       <c r="B46" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130800748</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130800737</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130800759</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130800763</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130800732</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130800736</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130800755</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130800751</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130800767</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130800746</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130800747</v>
       </c>
       <c r="B12" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130800740</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130800741</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,50 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800639</v>
+        <v>130800750</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488441</v>
+        <v>488188</v>
       </c>
       <c r="R15" t="n">
-        <v>6721177</v>
+        <v>6721096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,7 +2155,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2179,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800750</v>
+        <v>130800745</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488188</v>
+        <v>488254</v>
       </c>
       <c r="R16" t="n">
-        <v>6721096</v>
+        <v>6721190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2259,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,45 +2280,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800745</v>
+        <v>130800615</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>57053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488254</v>
+        <v>488401</v>
       </c>
       <c r="R17" t="n">
-        <v>6721190</v>
+        <v>6721155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2366,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800615</v>
+        <v>130800639</v>
       </c>
       <c r="B19" t="n">
-        <v>57053</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,27 +2515,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2545,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488401</v>
+        <v>488441</v>
       </c>
       <c r="R19" t="n">
-        <v>6721155</v>
+        <v>6721177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,6 +2598,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2617,45 +2617,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R20" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,7 +2692,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2697,7 +2702,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,50 +2729,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R21" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2839,7 +2839,7 @@
         <v>130800734</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>130800624</v>
       </c>
       <c r="B23" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>130800625</v>
       </c>
       <c r="B24" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,50 +3167,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800640</v>
+        <v>130800756</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488413</v>
+        <v>488470</v>
       </c>
       <c r="R25" t="n">
-        <v>6721172</v>
+        <v>6721165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,7 +3237,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3252,7 +3247,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,7 +3256,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3280,45 +3274,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800756</v>
+        <v>130800640</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488470</v>
+        <v>488413</v>
       </c>
       <c r="R26" t="n">
-        <v>6721165</v>
+        <v>6721172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,7 +3349,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3360,7 +3359,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,6 +3368,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>130800735</v>
       </c>
       <c r="B27" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>130800762</v>
       </c>
       <c r="B28" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>130800760</v>
       </c>
       <c r="B29" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>130800761</v>
       </c>
       <c r="B30" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>130800628</v>
       </c>
       <c r="B31" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>130800757</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>130800742</v>
       </c>
       <c r="B33" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>130800749</v>
       </c>
       <c r="B34" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,45 +4248,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B35" t="n">
-        <v>79220</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R35" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,50 +4360,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R36" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,7 +4470,7 @@
         <v>130800743</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>130800754</v>
       </c>
       <c r="B38" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>130800765</v>
       </c>
       <c r="B39" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>130800739</v>
       </c>
       <c r="B40" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>130800605</v>
       </c>
       <c r="B41" t="n">
-        <v>90820</v>
+        <v>90821</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>130800647</v>
       </c>
       <c r="B42" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>130800753</v>
       </c>
       <c r="B43" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>130800738</v>
       </c>
       <c r="B44" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>130800744</v>
       </c>
       <c r="B45" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>130800731</v>
       </c>
       <c r="B46" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -2066,45 +2066,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800750</v>
+        <v>130800639</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488188</v>
+        <v>488441</v>
       </c>
       <c r="R15" t="n">
-        <v>6721096</v>
+        <v>6721177</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2155,6 +2160,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2173,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800745</v>
+        <v>130800750</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2208,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488254</v>
+        <v>488188</v>
       </c>
       <c r="R16" t="n">
-        <v>6721190</v>
+        <v>6721096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,50 +2286,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800615</v>
+        <v>130800745</v>
       </c>
       <c r="B17" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488401</v>
+        <v>488254</v>
       </c>
       <c r="R17" t="n">
-        <v>6721155</v>
+        <v>6721190</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2356,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2366,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800769</v>
+        <v>130800615</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>57053</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,27 +2404,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2432,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488274</v>
+        <v>488401</v>
       </c>
       <c r="R18" t="n">
-        <v>6721118</v>
+        <v>6721155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2468,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2478,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800639</v>
+        <v>130800769</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2516,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488441</v>
+        <v>488274</v>
       </c>
       <c r="R19" t="n">
-        <v>6721177</v>
+        <v>6721118</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,7 +2599,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2617,50 +2617,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R20" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2702,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,45 +2724,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R21" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800625</v>
+        <v>130800756</v>
       </c>
       <c r="B24" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,39 +3066,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488400</v>
+        <v>488470</v>
       </c>
       <c r="R24" t="n">
-        <v>6721188</v>
+        <v>6721165</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3140,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,10 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800756</v>
+        <v>130800625</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,34 +3173,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488470</v>
+        <v>488400</v>
       </c>
       <c r="R25" t="n">
-        <v>6721165</v>
+        <v>6721188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4248,50 +4248,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R35" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4323,7 +4318,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4333,7 +4328,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,45 +4355,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B36" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R36" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -2066,50 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800639</v>
+        <v>130800750</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488441</v>
+        <v>488188</v>
       </c>
       <c r="R15" t="n">
-        <v>6721177</v>
+        <v>6721096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,7 +2155,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2179,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800750</v>
+        <v>130800745</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2214,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488188</v>
+        <v>488254</v>
       </c>
       <c r="R16" t="n">
-        <v>6721096</v>
+        <v>6721190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2259,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,45 +2280,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800745</v>
+        <v>130800769</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488254</v>
+        <v>488274</v>
       </c>
       <c r="R17" t="n">
-        <v>6721190</v>
+        <v>6721118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2366,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800769</v>
+        <v>130800639</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2545,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488274</v>
+        <v>488441</v>
       </c>
       <c r="R19" t="n">
-        <v>6721118</v>
+        <v>6721177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,6 +2598,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2617,45 +2617,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B20" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R20" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,7 +2692,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2697,7 +2702,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,50 +2729,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R21" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800734</v>
+        <v>130800624</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,34 +2847,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488276</v>
+        <v>488277</v>
       </c>
       <c r="R22" t="n">
-        <v>6721374</v>
+        <v>6721389</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2916,7 +2921,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2943,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800624</v>
+        <v>130800734</v>
       </c>
       <c r="B23" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2954,39 +2959,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488277</v>
+        <v>488276</v>
       </c>
       <c r="R23" t="n">
-        <v>6721389</v>
+        <v>6721374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,45 +3055,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800756</v>
+        <v>130800640</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488470</v>
+        <v>488413</v>
       </c>
       <c r="R24" t="n">
-        <v>6721165</v>
+        <v>6721172</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3135,7 +3140,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,6 +3149,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3274,50 +3280,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800640</v>
+        <v>130800756</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488413</v>
+        <v>488470</v>
       </c>
       <c r="R26" t="n">
-        <v>6721172</v>
+        <v>6721165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,7 +3350,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3360,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3369,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800762</v>
+        <v>130800760</v>
       </c>
       <c r="B28" t="n">
         <v>79221</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488314</v>
+        <v>488321</v>
       </c>
       <c r="R28" t="n">
-        <v>6721463</v>
+        <v>6721317</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,7 +3601,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800760</v>
+        <v>130800761</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488321</v>
+        <v>488353</v>
       </c>
       <c r="R29" t="n">
-        <v>6721317</v>
+        <v>6721338</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800761</v>
+        <v>130800628</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3719,34 +3719,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488353</v>
+        <v>488274</v>
       </c>
       <c r="R30" t="n">
-        <v>6721338</v>
+        <v>6721118</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3783,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3793,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800628</v>
+        <v>130800762</v>
       </c>
       <c r="B31" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,39 +3831,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488274</v>
+        <v>488314</v>
       </c>
       <c r="R31" t="n">
-        <v>6721118</v>
+        <v>6721463</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4248,45 +4248,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B35" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R35" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,50 +4360,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R36" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,7 +4467,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800743</v>
+        <v>130800754</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4505,7 +4505,7 @@
         <v>488261</v>
       </c>
       <c r="R37" t="n">
-        <v>6721212</v>
+        <v>6721112</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4574,7 +4574,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800754</v>
+        <v>130800743</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4612,7 +4612,7 @@
         <v>488261</v>
       </c>
       <c r="R38" t="n">
-        <v>6721112</v>
+        <v>6721212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800605</v>
+        <v>130800647</v>
       </c>
       <c r="B41" t="n">
-        <v>90821</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,34 +4906,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>889</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488425</v>
+        <v>488463</v>
       </c>
       <c r="R41" t="n">
-        <v>6721284</v>
+        <v>6721451</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4975,7 +4980,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I 200+ år gammal tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,10 +5012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800647</v>
+        <v>130800605</v>
       </c>
       <c r="B42" t="n">
-        <v>57861</v>
+        <v>90821</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,39 +5023,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>889</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488463</v>
+        <v>488425</v>
       </c>
       <c r="R42" t="n">
-        <v>6721451</v>
+        <v>6721284</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,7 +5082,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5087,12 +5092,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>I 200+ år gammal tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800753</v>
+        <v>130800738</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488256</v>
+        <v>488241</v>
       </c>
       <c r="R43" t="n">
-        <v>6721103</v>
+        <v>6721318</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800738</v>
+        <v>130800753</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488241</v>
+        <v>488256</v>
       </c>
       <c r="R44" t="n">
-        <v>6721318</v>
+        <v>6721103</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800767</v>
+        <v>130800740</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488277</v>
+        <v>488259</v>
       </c>
       <c r="R10" t="n">
-        <v>6721389</v>
+        <v>6721276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800746</v>
+        <v>130800767</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488260</v>
+        <v>488277</v>
       </c>
       <c r="R11" t="n">
-        <v>6721168</v>
+        <v>6721389</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800747</v>
+        <v>130800746</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488252</v>
+        <v>488260</v>
       </c>
       <c r="R12" t="n">
-        <v>6721136</v>
+        <v>6721168</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800740</v>
+        <v>130800747</v>
       </c>
       <c r="B13" t="n">
         <v>79221</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488259</v>
+        <v>488252</v>
       </c>
       <c r="R13" t="n">
-        <v>6721276</v>
+        <v>6721136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2617,50 +2617,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R20" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2702,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,45 +2724,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R21" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3927,7 +3927,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800757</v>
+        <v>130800742</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488454</v>
+        <v>488259</v>
       </c>
       <c r="R32" t="n">
-        <v>6721175</v>
+        <v>6721246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800742</v>
+        <v>130800757</v>
       </c>
       <c r="B33" t="n">
         <v>79221</v>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488259</v>
+        <v>488454</v>
       </c>
       <c r="R33" t="n">
-        <v>6721246</v>
+        <v>6721175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4248,50 +4248,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R35" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4323,7 +4318,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4333,7 +4328,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,45 +4355,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B36" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R36" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800738</v>
+        <v>130800753</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488241</v>
+        <v>488256</v>
       </c>
       <c r="R43" t="n">
-        <v>6721318</v>
+        <v>6721103</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800753</v>
+        <v>130800744</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488256</v>
+        <v>488254</v>
       </c>
       <c r="R44" t="n">
-        <v>6721103</v>
+        <v>6721200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800744</v>
+        <v>130800731</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488254</v>
+        <v>488290</v>
       </c>
       <c r="R45" t="n">
-        <v>6721200</v>
+        <v>6721380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800731</v>
+        <v>130800738</v>
       </c>
       <c r="B46" t="n">
         <v>79221</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488290</v>
+        <v>488241</v>
       </c>
       <c r="R46" t="n">
-        <v>6721380</v>
+        <v>6721318</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800740</v>
+        <v>130800767</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488259</v>
+        <v>488277</v>
       </c>
       <c r="R10" t="n">
-        <v>6721276</v>
+        <v>6721389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800767</v>
+        <v>130800746</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488277</v>
+        <v>488260</v>
       </c>
       <c r="R11" t="n">
-        <v>6721389</v>
+        <v>6721168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800746</v>
+        <v>130800747</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488260</v>
+        <v>488252</v>
       </c>
       <c r="R12" t="n">
-        <v>6721168</v>
+        <v>6721136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800747</v>
+        <v>130800740</v>
       </c>
       <c r="B13" t="n">
         <v>79221</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488252</v>
+        <v>488259</v>
       </c>
       <c r="R13" t="n">
-        <v>6721136</v>
+        <v>6721276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800769</v>
+        <v>130800615</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>57053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,27 +2291,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488274</v>
+        <v>488401</v>
       </c>
       <c r="R17" t="n">
-        <v>6721118</v>
+        <v>6721155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800615</v>
+        <v>130800769</v>
       </c>
       <c r="B18" t="n">
-        <v>57053</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,27 +2403,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488401</v>
+        <v>488274</v>
       </c>
       <c r="R18" t="n">
-        <v>6721155</v>
+        <v>6721118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800624</v>
+        <v>130800734</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,39 +2847,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488277</v>
+        <v>488276</v>
       </c>
       <c r="R22" t="n">
-        <v>6721389</v>
+        <v>6721374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2921,7 +2916,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800734</v>
+        <v>130800624</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,34 +2954,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488276</v>
+        <v>488277</v>
       </c>
       <c r="R23" t="n">
-        <v>6721374</v>
+        <v>6721389</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,50 +3055,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800640</v>
+        <v>130800756</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488413</v>
+        <v>488470</v>
       </c>
       <c r="R24" t="n">
-        <v>6721172</v>
+        <v>6721165</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3140,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,7 +3144,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3280,45 +3274,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800756</v>
+        <v>130800640</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488470</v>
+        <v>488413</v>
       </c>
       <c r="R26" t="n">
-        <v>6721165</v>
+        <v>6721172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,7 +3349,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3360,7 +3359,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,6 +3368,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800760</v>
+        <v>130800762</v>
       </c>
       <c r="B28" t="n">
         <v>79221</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488321</v>
+        <v>488314</v>
       </c>
       <c r="R28" t="n">
-        <v>6721317</v>
+        <v>6721463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,7 +3601,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800761</v>
+        <v>130800760</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488353</v>
+        <v>488321</v>
       </c>
       <c r="R29" t="n">
-        <v>6721338</v>
+        <v>6721317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800628</v>
+        <v>130800761</v>
       </c>
       <c r="B30" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3719,39 +3719,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488274</v>
+        <v>488353</v>
       </c>
       <c r="R30" t="n">
-        <v>6721118</v>
+        <v>6721338</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3793,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800762</v>
+        <v>130800628</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,34 +3826,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488314</v>
+        <v>488274</v>
       </c>
       <c r="R31" t="n">
-        <v>6721463</v>
+        <v>6721118</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,7 +3927,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800742</v>
+        <v>130800757</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488259</v>
+        <v>488454</v>
       </c>
       <c r="R32" t="n">
-        <v>6721246</v>
+        <v>6721175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800757</v>
+        <v>130800742</v>
       </c>
       <c r="B33" t="n">
         <v>79221</v>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488454</v>
+        <v>488259</v>
       </c>
       <c r="R33" t="n">
-        <v>6721175</v>
+        <v>6721246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4467,7 +4467,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800754</v>
+        <v>130800743</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4505,7 +4505,7 @@
         <v>488261</v>
       </c>
       <c r="R37" t="n">
-        <v>6721112</v>
+        <v>6721212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4574,7 +4574,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800743</v>
+        <v>130800754</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4612,7 +4612,7 @@
         <v>488261</v>
       </c>
       <c r="R38" t="n">
-        <v>6721212</v>
+        <v>6721112</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800753</v>
+        <v>130800744</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488256</v>
+        <v>488254</v>
       </c>
       <c r="R43" t="n">
-        <v>6721103</v>
+        <v>6721200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800744</v>
+        <v>130800753</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488254</v>
+        <v>488256</v>
       </c>
       <c r="R44" t="n">
-        <v>6721200</v>
+        <v>6721103</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800731</v>
+        <v>130800738</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488290</v>
+        <v>488241</v>
       </c>
       <c r="R45" t="n">
-        <v>6721380</v>
+        <v>6721318</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800738</v>
+        <v>130800731</v>
       </c>
       <c r="B46" t="n">
         <v>79221</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488241</v>
+        <v>488290</v>
       </c>
       <c r="R46" t="n">
-        <v>6721318</v>
+        <v>6721380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130800737</v>
+        <v>130800759</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488255</v>
+        <v>488315</v>
       </c>
       <c r="R3" t="n">
-        <v>6721336</v>
+        <v>6721292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130800759</v>
+        <v>130800737</v>
       </c>
       <c r="B4" t="n">
         <v>79221</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488315</v>
+        <v>488255</v>
       </c>
       <c r="R4" t="n">
-        <v>6721292</v>
+        <v>6721336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2066,45 +2066,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800750</v>
+        <v>130800639</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488188</v>
+        <v>488441</v>
       </c>
       <c r="R15" t="n">
-        <v>6721096</v>
+        <v>6721177</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2155,6 +2160,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2173,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800745</v>
+        <v>130800750</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2208,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488254</v>
+        <v>488188</v>
       </c>
       <c r="R16" t="n">
-        <v>6721190</v>
+        <v>6721096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,50 +2286,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800615</v>
+        <v>130800745</v>
       </c>
       <c r="B17" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488401</v>
+        <v>488254</v>
       </c>
       <c r="R17" t="n">
-        <v>6721155</v>
+        <v>6721190</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2356,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2366,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800639</v>
+        <v>130800615</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>57053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,27 +2516,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2544,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488441</v>
+        <v>488401</v>
       </c>
       <c r="R19" t="n">
-        <v>6721177</v>
+        <v>6721155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,7 +2599,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800734</v>
+        <v>130800624</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,34 +2847,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488276</v>
+        <v>488277</v>
       </c>
       <c r="R22" t="n">
-        <v>6721374</v>
+        <v>6721389</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2916,7 +2921,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2943,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800624</v>
+        <v>130800734</v>
       </c>
       <c r="B23" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2954,39 +2959,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488277</v>
+        <v>488276</v>
       </c>
       <c r="R23" t="n">
-        <v>6721389</v>
+        <v>6721374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3601,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800760</v>
+        <v>130800628</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,34 +3612,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488321</v>
+        <v>488274</v>
       </c>
       <c r="R29" t="n">
-        <v>6721317</v>
+        <v>6721118</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3671,7 +3676,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3681,7 +3686,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,7 +3713,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800761</v>
+        <v>130800760</v>
       </c>
       <c r="B30" t="n">
         <v>79221</v>
@@ -3743,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488353</v>
+        <v>488321</v>
       </c>
       <c r="R30" t="n">
-        <v>6721338</v>
+        <v>6721317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3783,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3793,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800628</v>
+        <v>130800761</v>
       </c>
       <c r="B31" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,39 +3831,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488274</v>
+        <v>488353</v>
       </c>
       <c r="R31" t="n">
-        <v>6721118</v>
+        <v>6721338</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800744</v>
+        <v>130800753</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488254</v>
+        <v>488256</v>
       </c>
       <c r="R43" t="n">
-        <v>6721200</v>
+        <v>6721103</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800753</v>
+        <v>130800738</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488256</v>
+        <v>488241</v>
       </c>
       <c r="R44" t="n">
-        <v>6721103</v>
+        <v>6721318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800738</v>
+        <v>130800744</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488241</v>
+        <v>488254</v>
       </c>
       <c r="R45" t="n">
-        <v>6721318</v>
+        <v>6721200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130800748</v>
+        <v>130800737</v>
       </c>
       <c r="B2" t="n">
         <v>79221</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488228</v>
+        <v>488255</v>
       </c>
       <c r="R2" t="n">
-        <v>6721082</v>
+        <v>6721336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130800759</v>
+        <v>130800748</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488315</v>
+        <v>488228</v>
       </c>
       <c r="R3" t="n">
-        <v>6721292</v>
+        <v>6721082</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130800737</v>
+        <v>130800759</v>
       </c>
       <c r="B4" t="n">
         <v>79221</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488255</v>
+        <v>488315</v>
       </c>
       <c r="R4" t="n">
-        <v>6721336</v>
+        <v>6721292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130800732</v>
+        <v>130800755</v>
       </c>
       <c r="B6" t="n">
         <v>79221</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488287</v>
+        <v>488272</v>
       </c>
       <c r="R6" t="n">
-        <v>6721384</v>
+        <v>6721114</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800736</v>
+        <v>130800732</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488253</v>
+        <v>488287</v>
       </c>
       <c r="R7" t="n">
-        <v>6721360</v>
+        <v>6721384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800755</v>
+        <v>130800736</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488272</v>
+        <v>488253</v>
       </c>
       <c r="R8" t="n">
-        <v>6721114</v>
+        <v>6721360</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800747</v>
+        <v>130800740</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488252</v>
+        <v>488259</v>
       </c>
       <c r="R12" t="n">
-        <v>6721136</v>
+        <v>6721276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800740</v>
+        <v>130800747</v>
       </c>
       <c r="B13" t="n">
         <v>79221</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488259</v>
+        <v>488252</v>
       </c>
       <c r="R13" t="n">
-        <v>6721276</v>
+        <v>6721136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,50 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800639</v>
+        <v>130800750</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488441</v>
+        <v>488188</v>
       </c>
       <c r="R15" t="n">
-        <v>6721177</v>
+        <v>6721096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,7 +2155,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2179,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800750</v>
+        <v>130800745</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2214,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488188</v>
+        <v>488254</v>
       </c>
       <c r="R16" t="n">
-        <v>6721096</v>
+        <v>6721190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2259,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,45 +2280,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800745</v>
+        <v>130800769</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488254</v>
+        <v>488274</v>
       </c>
       <c r="R17" t="n">
-        <v>6721190</v>
+        <v>6721118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2366,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2393,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800769</v>
+        <v>130800615</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>57053</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,27 +2403,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2433,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488274</v>
+        <v>488401</v>
       </c>
       <c r="R18" t="n">
-        <v>6721118</v>
+        <v>6721155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2478,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800615</v>
+        <v>130800639</v>
       </c>
       <c r="B19" t="n">
-        <v>57053</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,27 +2515,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2545,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488401</v>
+        <v>488441</v>
       </c>
       <c r="R19" t="n">
-        <v>6721155</v>
+        <v>6721177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,6 +2598,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800756</v>
+        <v>130800625</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,34 +3066,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488470</v>
+        <v>488400</v>
       </c>
       <c r="R24" t="n">
-        <v>6721165</v>
+        <v>6721188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3135,7 +3140,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,38 +3167,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800625</v>
+        <v>130800640</v>
       </c>
       <c r="B25" t="n">
-        <v>57861</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3202,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488400</v>
+        <v>488413</v>
       </c>
       <c r="R25" t="n">
-        <v>6721188</v>
+        <v>6721172</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,7 +3242,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3247,7 +3252,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,6 +3261,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3274,50 +3280,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800640</v>
+        <v>130800756</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488413</v>
+        <v>488470</v>
       </c>
       <c r="R26" t="n">
-        <v>6721172</v>
+        <v>6721165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,7 +3350,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3360,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3369,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800762</v>
+        <v>130800628</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,34 +3505,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488314</v>
+        <v>488274</v>
       </c>
       <c r="R28" t="n">
-        <v>6721463</v>
+        <v>6721118</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3569,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3574,7 +3579,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,10 +3606,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800628</v>
+        <v>130800762</v>
       </c>
       <c r="B29" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,39 +3617,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488274</v>
+        <v>488314</v>
       </c>
       <c r="R29" t="n">
-        <v>6721118</v>
+        <v>6721463</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4574,7 +4574,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800754</v>
+        <v>130800765</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488261</v>
+        <v>488294</v>
       </c>
       <c r="R38" t="n">
-        <v>6721112</v>
+        <v>6721432</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4681,7 +4681,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800765</v>
+        <v>130800754</v>
       </c>
       <c r="B39" t="n">
         <v>79221</v>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488294</v>
+        <v>488261</v>
       </c>
       <c r="R39" t="n">
-        <v>6721432</v>
+        <v>6721112</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130800737</v>
+        <v>130800748</v>
       </c>
       <c r="B2" t="n">
         <v>79221</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488255</v>
+        <v>488228</v>
       </c>
       <c r="R2" t="n">
-        <v>6721336</v>
+        <v>6721082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130800748</v>
+        <v>130800737</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488228</v>
+        <v>488255</v>
       </c>
       <c r="R3" t="n">
-        <v>6721082</v>
+        <v>6721336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130800755</v>
+        <v>130800732</v>
       </c>
       <c r="B6" t="n">
         <v>79221</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488272</v>
+        <v>488287</v>
       </c>
       <c r="R6" t="n">
-        <v>6721114</v>
+        <v>6721384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800732</v>
+        <v>130800736</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488287</v>
+        <v>488253</v>
       </c>
       <c r="R7" t="n">
-        <v>6721384</v>
+        <v>6721360</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800736</v>
+        <v>130800755</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488253</v>
+        <v>488272</v>
       </c>
       <c r="R8" t="n">
-        <v>6721360</v>
+        <v>6721114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800740</v>
+        <v>130800747</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488259</v>
+        <v>488252</v>
       </c>
       <c r="R12" t="n">
-        <v>6721276</v>
+        <v>6721136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800747</v>
+        <v>130800740</v>
       </c>
       <c r="B13" t="n">
         <v>79221</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488252</v>
+        <v>488259</v>
       </c>
       <c r="R13" t="n">
-        <v>6721136</v>
+        <v>6721276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800769</v>
+        <v>130800615</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>57053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,27 +2291,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488274</v>
+        <v>488401</v>
       </c>
       <c r="R17" t="n">
-        <v>6721118</v>
+        <v>6721155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800615</v>
+        <v>130800769</v>
       </c>
       <c r="B18" t="n">
-        <v>57053</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,27 +2403,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488401</v>
+        <v>488274</v>
       </c>
       <c r="R18" t="n">
-        <v>6721155</v>
+        <v>6721118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3055,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800625</v>
+        <v>130800756</v>
       </c>
       <c r="B24" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,39 +3066,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488400</v>
+        <v>488470</v>
       </c>
       <c r="R24" t="n">
-        <v>6721188</v>
+        <v>6721165</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3140,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,38 +3162,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800640</v>
+        <v>130800625</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>57861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3207,10 +3202,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488413</v>
+        <v>488400</v>
       </c>
       <c r="R25" t="n">
-        <v>6721172</v>
+        <v>6721188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,7 +3237,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3252,7 +3247,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,7 +3256,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3280,45 +3274,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800756</v>
+        <v>130800640</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488470</v>
+        <v>488413</v>
       </c>
       <c r="R26" t="n">
-        <v>6721165</v>
+        <v>6721172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,7 +3349,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3360,7 +3359,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,6 +3368,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800628</v>
+        <v>130800762</v>
       </c>
       <c r="B28" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,39 +3505,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488274</v>
+        <v>488314</v>
       </c>
       <c r="R28" t="n">
-        <v>6721118</v>
+        <v>6721463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3569,7 +3564,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3579,7 +3574,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3606,7 +3601,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800762</v>
+        <v>130800760</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488314</v>
+        <v>488321</v>
       </c>
       <c r="R29" t="n">
-        <v>6721463</v>
+        <v>6721317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3671,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3686,7 +3681,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,7 +3708,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800760</v>
+        <v>130800761</v>
       </c>
       <c r="B30" t="n">
         <v>79221</v>
@@ -3748,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488321</v>
+        <v>488353</v>
       </c>
       <c r="R30" t="n">
-        <v>6721317</v>
+        <v>6721338</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3793,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800761</v>
+        <v>130800628</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,34 +3826,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488353</v>
+        <v>488274</v>
       </c>
       <c r="R31" t="n">
-        <v>6721338</v>
+        <v>6721118</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4248,45 +4248,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B35" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R35" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,50 +4360,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R36" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,7 +4574,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130800765</v>
+        <v>130800754</v>
       </c>
       <c r="B38" t="n">
         <v>79221</v>
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488294</v>
+        <v>488261</v>
       </c>
       <c r="R38" t="n">
-        <v>6721432</v>
+        <v>6721112</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4681,7 +4681,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800754</v>
+        <v>130800765</v>
       </c>
       <c r="B39" t="n">
         <v>79221</v>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488261</v>
+        <v>488294</v>
       </c>
       <c r="R39" t="n">
-        <v>6721112</v>
+        <v>6721432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800647</v>
+        <v>130800605</v>
       </c>
       <c r="B41" t="n">
-        <v>57861</v>
+        <v>90821</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,39 +4906,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>889</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488463</v>
+        <v>488425</v>
       </c>
       <c r="R41" t="n">
-        <v>6721451</v>
+        <v>6721284</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,12 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>I 200+ år gammal tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5012,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800605</v>
+        <v>130800647</v>
       </c>
       <c r="B42" t="n">
-        <v>90821</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5023,34 +5013,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>889</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488425</v>
+        <v>488463</v>
       </c>
       <c r="R42" t="n">
-        <v>6721284</v>
+        <v>6721451</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5082,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5092,7 +5087,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>I 200+ år gammal tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800753</v>
+        <v>130800731</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488256</v>
+        <v>488290</v>
       </c>
       <c r="R43" t="n">
-        <v>6721103</v>
+        <v>6721380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800738</v>
+        <v>130800753</v>
       </c>
       <c r="B44" t="n">
         <v>79221</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488241</v>
+        <v>488256</v>
       </c>
       <c r="R44" t="n">
-        <v>6721318</v>
+        <v>6721103</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800744</v>
+        <v>130800738</v>
       </c>
       <c r="B45" t="n">
         <v>79221</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488254</v>
+        <v>488241</v>
       </c>
       <c r="R45" t="n">
-        <v>6721200</v>
+        <v>6721318</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800731</v>
+        <v>130800744</v>
       </c>
       <c r="B46" t="n">
         <v>79221</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488290</v>
+        <v>488254</v>
       </c>
       <c r="R46" t="n">
-        <v>6721380</v>
+        <v>6721200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130800737</v>
+        <v>130800748</v>
       </c>
       <c r="B2" t="n">
         <v>79243</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488255</v>
+        <v>488228</v>
       </c>
       <c r="R2" t="n">
-        <v>6721336</v>
+        <v>6721082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130800759</v>
+        <v>130800737</v>
       </c>
       <c r="B3" t="n">
         <v>79243</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488315</v>
+        <v>488255</v>
       </c>
       <c r="R3" t="n">
-        <v>6721292</v>
+        <v>6721336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130800748</v>
+        <v>130800759</v>
       </c>
       <c r="B4" t="n">
         <v>79243</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488228</v>
+        <v>488315</v>
       </c>
       <c r="R4" t="n">
-        <v>6721082</v>
+        <v>6721292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130800736</v>
+        <v>130800763</v>
       </c>
       <c r="B5" t="n">
         <v>79243</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488253</v>
+        <v>488309</v>
       </c>
       <c r="R5" t="n">
-        <v>6721360</v>
+        <v>6721442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130800755</v>
+        <v>130800736</v>
       </c>
       <c r="B6" t="n">
         <v>79243</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488272</v>
+        <v>488253</v>
       </c>
       <c r="R6" t="n">
-        <v>6721114</v>
+        <v>6721360</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800763</v>
+        <v>130800732</v>
       </c>
       <c r="B7" t="n">
         <v>79243</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488309</v>
+        <v>488287</v>
       </c>
       <c r="R7" t="n">
-        <v>6721442</v>
+        <v>6721384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130800732</v>
+        <v>130800755</v>
       </c>
       <c r="B8" t="n">
         <v>79243</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488287</v>
+        <v>488272</v>
       </c>
       <c r="R8" t="n">
-        <v>6721384</v>
+        <v>6721114</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800746</v>
+        <v>130800747</v>
       </c>
       <c r="B11" t="n">
         <v>79243</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488260</v>
+        <v>488252</v>
       </c>
       <c r="R11" t="n">
-        <v>6721168</v>
+        <v>6721136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800747</v>
+        <v>130800740</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488252</v>
+        <v>488259</v>
       </c>
       <c r="R12" t="n">
-        <v>6721136</v>
+        <v>6721276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800740</v>
+        <v>130800746</v>
       </c>
       <c r="B13" t="n">
         <v>79243</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488259</v>
+        <v>488260</v>
       </c>
       <c r="R13" t="n">
-        <v>6721276</v>
+        <v>6721168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800769</v>
+        <v>130800639</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488274</v>
+        <v>488441</v>
       </c>
       <c r="R15" t="n">
-        <v>6721118</v>
+        <v>6721177</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,6 +2160,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2178,50 +2179,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800615</v>
+        <v>130800750</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>79243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488401</v>
+        <v>488188</v>
       </c>
       <c r="R16" t="n">
-        <v>6721155</v>
+        <v>6721096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2249,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2259,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,50 +2286,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800639</v>
+        <v>130800745</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488441</v>
+        <v>488254</v>
       </c>
       <c r="R17" t="n">
-        <v>6721177</v>
+        <v>6721190</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2356,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2366,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,7 +2375,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2403,45 +2393,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800750</v>
+        <v>130800769</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488188</v>
+        <v>488274</v>
       </c>
       <c r="R18" t="n">
-        <v>6721096</v>
+        <v>6721118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,7 +2468,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2483,7 +2478,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,45 +2505,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800745</v>
+        <v>130800615</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>57073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488254</v>
+        <v>488401</v>
       </c>
       <c r="R19" t="n">
-        <v>6721190</v>
+        <v>6721155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,45 +2617,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R20" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,7 +2692,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2697,7 +2702,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,50 +2729,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R21" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3494,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800760</v>
+        <v>130800761</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488321</v>
+        <v>488353</v>
       </c>
       <c r="R28" t="n">
-        <v>6721317</v>
+        <v>6721338</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800762</v>
+        <v>130800628</v>
       </c>
       <c r="B29" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,34 +3612,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488314</v>
+        <v>488274</v>
       </c>
       <c r="R29" t="n">
-        <v>6721463</v>
+        <v>6721118</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3671,7 +3676,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3681,7 +3686,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,7 +3713,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800761</v>
+        <v>130800762</v>
       </c>
       <c r="B30" t="n">
         <v>79243</v>
@@ -3743,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488353</v>
+        <v>488314</v>
       </c>
       <c r="R30" t="n">
-        <v>6721338</v>
+        <v>6721463</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3783,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3793,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,10 +3820,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800628</v>
+        <v>130800760</v>
       </c>
       <c r="B31" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3826,39 +3831,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488274</v>
+        <v>488321</v>
       </c>
       <c r="R31" t="n">
-        <v>6721118</v>
+        <v>6721317</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800744</v>
+        <v>130800753</v>
       </c>
       <c r="B43" t="n">
         <v>79243</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488254</v>
+        <v>488256</v>
       </c>
       <c r="R43" t="n">
-        <v>6721200</v>
+        <v>6721103</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800731</v>
+        <v>130800744</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488290</v>
+        <v>488254</v>
       </c>
       <c r="R44" t="n">
-        <v>6721380</v>
+        <v>6721200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800753</v>
+        <v>130800731</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488256</v>
+        <v>488290</v>
       </c>
       <c r="R45" t="n">
-        <v>6721103</v>
+        <v>6721380</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800747</v>
+        <v>130800746</v>
       </c>
       <c r="B11" t="n">
         <v>79243</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488252</v>
+        <v>488260</v>
       </c>
       <c r="R11" t="n">
-        <v>6721136</v>
+        <v>6721168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800740</v>
+        <v>130800747</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488259</v>
+        <v>488252</v>
       </c>
       <c r="R12" t="n">
-        <v>6721276</v>
+        <v>6721136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800746</v>
+        <v>130800740</v>
       </c>
       <c r="B13" t="n">
         <v>79243</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488260</v>
+        <v>488259</v>
       </c>
       <c r="R13" t="n">
-        <v>6721168</v>
+        <v>6721276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800639</v>
+        <v>130800769</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488441</v>
+        <v>488274</v>
       </c>
       <c r="R15" t="n">
-        <v>6721177</v>
+        <v>6721118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,7 +2160,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2179,45 +2178,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800750</v>
+        <v>130800615</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>57073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488188</v>
+        <v>488401</v>
       </c>
       <c r="R16" t="n">
-        <v>6721096</v>
+        <v>6721155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2259,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,45 +2290,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800745</v>
+        <v>130800639</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488254</v>
+        <v>488441</v>
       </c>
       <c r="R17" t="n">
-        <v>6721190</v>
+        <v>6721177</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2366,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,6 +2384,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2393,50 +2403,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800769</v>
+        <v>130800750</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488274</v>
+        <v>488188</v>
       </c>
       <c r="R18" t="n">
-        <v>6721118</v>
+        <v>6721096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,7 +2473,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2478,7 +2483,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,50 +2510,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800615</v>
+        <v>130800745</v>
       </c>
       <c r="B19" t="n">
-        <v>57073</v>
+        <v>79243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488401</v>
+        <v>488254</v>
       </c>
       <c r="R19" t="n">
-        <v>6721155</v>
+        <v>6721190</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130800748</v>
+        <v>130800759</v>
       </c>
       <c r="B2" t="n">
         <v>79243</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488228</v>
+        <v>488315</v>
       </c>
       <c r="R2" t="n">
-        <v>6721082</v>
+        <v>6721292</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130800737</v>
+        <v>130800748</v>
       </c>
       <c r="B3" t="n">
         <v>79243</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488255</v>
+        <v>488228</v>
       </c>
       <c r="R3" t="n">
-        <v>6721336</v>
+        <v>6721082</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130800759</v>
+        <v>130800737</v>
       </c>
       <c r="B4" t="n">
         <v>79243</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488315</v>
+        <v>488255</v>
       </c>
       <c r="R4" t="n">
-        <v>6721292</v>
+        <v>6721336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130800763</v>
+        <v>130800736</v>
       </c>
       <c r="B5" t="n">
         <v>79243</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488309</v>
+        <v>488253</v>
       </c>
       <c r="R5" t="n">
-        <v>6721442</v>
+        <v>6721360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130800736</v>
+        <v>130800763</v>
       </c>
       <c r="B6" t="n">
         <v>79243</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488253</v>
+        <v>488309</v>
       </c>
       <c r="R6" t="n">
-        <v>6721360</v>
+        <v>6721442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800767</v>
+        <v>130800740</v>
       </c>
       <c r="B10" t="n">
         <v>79243</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488277</v>
+        <v>488259</v>
       </c>
       <c r="R10" t="n">
-        <v>6721389</v>
+        <v>6721276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800740</v>
+        <v>130800767</v>
       </c>
       <c r="B13" t="n">
         <v>79243</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488259</v>
+        <v>488277</v>
       </c>
       <c r="R13" t="n">
-        <v>6721276</v>
+        <v>6721389</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,50 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800769</v>
+        <v>130800750</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488274</v>
+        <v>488188</v>
       </c>
       <c r="R15" t="n">
-        <v>6721118</v>
+        <v>6721096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800615</v>
+        <v>130800639</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,27 +2184,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2218,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488401</v>
+        <v>488441</v>
       </c>
       <c r="R16" t="n">
-        <v>6721155</v>
+        <v>6721177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,6 +2267,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2290,50 +2286,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800639</v>
+        <v>130800745</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488441</v>
+        <v>488254</v>
       </c>
       <c r="R17" t="n">
-        <v>6721177</v>
+        <v>6721190</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2356,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2366,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,7 +2375,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2403,45 +2393,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800750</v>
+        <v>130800615</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>57073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488188</v>
+        <v>488401</v>
       </c>
       <c r="R18" t="n">
-        <v>6721096</v>
+        <v>6721155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,7 +2468,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2483,7 +2478,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,45 +2505,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800745</v>
+        <v>130800769</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488254</v>
+        <v>488274</v>
       </c>
       <c r="R19" t="n">
-        <v>6721190</v>
+        <v>6721118</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,50 +2617,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R20" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2702,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,45 +2724,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R21" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800734</v>
+        <v>130800624</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,34 +2847,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488276</v>
+        <v>488277</v>
       </c>
       <c r="R22" t="n">
-        <v>6721374</v>
+        <v>6721389</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2916,7 +2921,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2943,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800624</v>
+        <v>130800734</v>
       </c>
       <c r="B23" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2954,39 +2959,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488277</v>
+        <v>488276</v>
       </c>
       <c r="R23" t="n">
-        <v>6721389</v>
+        <v>6721374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,45 +3055,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800756</v>
+        <v>130800640</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488470</v>
+        <v>488413</v>
       </c>
       <c r="R24" t="n">
-        <v>6721165</v>
+        <v>6721172</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,7 +3130,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3135,7 +3140,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,6 +3149,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3274,50 +3280,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800640</v>
+        <v>130800756</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488413</v>
+        <v>488470</v>
       </c>
       <c r="R26" t="n">
-        <v>6721172</v>
+        <v>6721165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,7 +3350,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3360,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3369,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800761</v>
+        <v>130800628</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,34 +3505,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488353</v>
+        <v>488274</v>
       </c>
       <c r="R28" t="n">
-        <v>6721338</v>
+        <v>6721118</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3569,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3574,7 +3579,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,10 +3606,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800628</v>
+        <v>130800760</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,39 +3617,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488274</v>
+        <v>488321</v>
       </c>
       <c r="R29" t="n">
-        <v>6721118</v>
+        <v>6721317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800762</v>
+        <v>130800761</v>
       </c>
       <c r="B30" t="n">
         <v>79243</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488314</v>
+        <v>488353</v>
       </c>
       <c r="R30" t="n">
-        <v>6721463</v>
+        <v>6721338</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,7 +3820,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800760</v>
+        <v>130800762</v>
       </c>
       <c r="B31" t="n">
         <v>79243</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488321</v>
+        <v>488314</v>
       </c>
       <c r="R31" t="n">
-        <v>6721317</v>
+        <v>6721463</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,7 +3927,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800757</v>
+        <v>130800742</v>
       </c>
       <c r="B32" t="n">
         <v>79243</v>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488454</v>
+        <v>488259</v>
       </c>
       <c r="R32" t="n">
-        <v>6721175</v>
+        <v>6721246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800742</v>
+        <v>130800757</v>
       </c>
       <c r="B33" t="n">
         <v>79243</v>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488259</v>
+        <v>488454</v>
       </c>
       <c r="R33" t="n">
-        <v>6721246</v>
+        <v>6721175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4248,45 +4248,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R35" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,50 +4360,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R36" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,7 +4467,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800743</v>
+        <v>130800765</v>
       </c>
       <c r="B37" t="n">
         <v>79243</v>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488261</v>
+        <v>488294</v>
       </c>
       <c r="R37" t="n">
-        <v>6721212</v>
+        <v>6721432</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4681,7 +4681,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800765</v>
+        <v>130800743</v>
       </c>
       <c r="B39" t="n">
         <v>79243</v>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488294</v>
+        <v>488261</v>
       </c>
       <c r="R39" t="n">
-        <v>6721432</v>
+        <v>6721212</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130800647</v>
+        <v>130800605</v>
       </c>
       <c r="B41" t="n">
-        <v>57881</v>
+        <v>90845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,39 +4906,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>889</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488463</v>
+        <v>488425</v>
       </c>
       <c r="R41" t="n">
-        <v>6721451</v>
+        <v>6721284</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,7 +4965,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4980,12 +4975,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>I 200+ år gammal tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5012,10 +5002,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130800605</v>
+        <v>130800647</v>
       </c>
       <c r="B42" t="n">
-        <v>90845</v>
+        <v>57881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5023,34 +5013,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>889</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488425</v>
+        <v>488463</v>
       </c>
       <c r="R42" t="n">
-        <v>6721284</v>
+        <v>6721451</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5082,7 +5077,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5092,7 +5087,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>I 200+ år gammal tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800753</v>
+        <v>130800738</v>
       </c>
       <c r="B43" t="n">
         <v>79243</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488256</v>
+        <v>488241</v>
       </c>
       <c r="R43" t="n">
-        <v>6721103</v>
+        <v>6721318</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800744</v>
+        <v>130800753</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488254</v>
+        <v>488256</v>
       </c>
       <c r="R44" t="n">
-        <v>6721200</v>
+        <v>6721103</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800738</v>
+        <v>130800744</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488241</v>
+        <v>488254</v>
       </c>
       <c r="R46" t="n">
-        <v>6721318</v>
+        <v>6721200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130800759</v>
+        <v>130800737</v>
       </c>
       <c r="B2" t="n">
         <v>79243</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488315</v>
+        <v>488255</v>
       </c>
       <c r="R2" t="n">
-        <v>6721292</v>
+        <v>6721336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130800737</v>
+        <v>130800759</v>
       </c>
       <c r="B4" t="n">
         <v>79243</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488255</v>
+        <v>488315</v>
       </c>
       <c r="R4" t="n">
-        <v>6721336</v>
+        <v>6721292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130800736</v>
+        <v>130800763</v>
       </c>
       <c r="B5" t="n">
         <v>79243</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488253</v>
+        <v>488309</v>
       </c>
       <c r="R5" t="n">
-        <v>6721360</v>
+        <v>6721442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130800763</v>
+        <v>130800732</v>
       </c>
       <c r="B6" t="n">
         <v>79243</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488309</v>
+        <v>488287</v>
       </c>
       <c r="R6" t="n">
-        <v>6721442</v>
+        <v>6721384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130800732</v>
+        <v>130800736</v>
       </c>
       <c r="B7" t="n">
         <v>79243</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488287</v>
+        <v>488253</v>
       </c>
       <c r="R7" t="n">
-        <v>6721384</v>
+        <v>6721360</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800740</v>
+        <v>130800747</v>
       </c>
       <c r="B10" t="n">
         <v>79243</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488259</v>
+        <v>488252</v>
       </c>
       <c r="R10" t="n">
-        <v>6721276</v>
+        <v>6721136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800746</v>
+        <v>130800740</v>
       </c>
       <c r="B11" t="n">
         <v>79243</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488260</v>
+        <v>488259</v>
       </c>
       <c r="R11" t="n">
-        <v>6721168</v>
+        <v>6721276</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800747</v>
+        <v>130800767</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488252</v>
+        <v>488277</v>
       </c>
       <c r="R12" t="n">
-        <v>6721136</v>
+        <v>6721389</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800767</v>
+        <v>130800746</v>
       </c>
       <c r="B13" t="n">
         <v>79243</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488277</v>
+        <v>488260</v>
       </c>
       <c r="R13" t="n">
-        <v>6721389</v>
+        <v>6721168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,45 +2066,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800750</v>
+        <v>130800639</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488188</v>
+        <v>488441</v>
       </c>
       <c r="R15" t="n">
-        <v>6721096</v>
+        <v>6721177</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2155,6 +2160,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2173,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800639</v>
+        <v>130800769</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488441</v>
+        <v>488274</v>
       </c>
       <c r="R16" t="n">
-        <v>6721177</v>
+        <v>6721118</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2254,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2264,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2267,7 +2273,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,45 +2291,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800745</v>
+        <v>130800615</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>57073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488254</v>
+        <v>488401</v>
       </c>
       <c r="R17" t="n">
-        <v>6721190</v>
+        <v>6721155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,7 +2366,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2366,7 +2376,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2393,50 +2403,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800615</v>
+        <v>130800750</v>
       </c>
       <c r="B18" t="n">
-        <v>57073</v>
+        <v>79243</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488401</v>
+        <v>488188</v>
       </c>
       <c r="R18" t="n">
-        <v>6721155</v>
+        <v>6721096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,7 +2473,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2478,7 +2483,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2505,50 +2510,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800769</v>
+        <v>130800745</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488274</v>
+        <v>488254</v>
       </c>
       <c r="R19" t="n">
-        <v>6721118</v>
+        <v>6721190</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,45 +2617,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R20" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,7 +2692,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2697,7 +2702,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,50 +2729,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R21" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800624</v>
+        <v>130800734</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,39 +2847,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488277</v>
+        <v>488276</v>
       </c>
       <c r="R22" t="n">
-        <v>6721389</v>
+        <v>6721374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2921,7 +2916,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800734</v>
+        <v>130800624</v>
       </c>
       <c r="B23" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,34 +2954,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488276</v>
+        <v>488277</v>
       </c>
       <c r="R23" t="n">
-        <v>6721374</v>
+        <v>6721389</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,38 +3055,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800640</v>
+        <v>130800625</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488413</v>
+        <v>488400</v>
       </c>
       <c r="R24" t="n">
-        <v>6721172</v>
+        <v>6721188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,7 +3149,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3168,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800625</v>
+        <v>130800756</v>
       </c>
       <c r="B25" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3179,39 +3178,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488400</v>
+        <v>488470</v>
       </c>
       <c r="R25" t="n">
-        <v>6721188</v>
+        <v>6721165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,7 +3237,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3253,7 +3247,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3280,45 +3274,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800756</v>
+        <v>130800640</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488470</v>
+        <v>488413</v>
       </c>
       <c r="R26" t="n">
-        <v>6721165</v>
+        <v>6721172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,7 +3349,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3360,7 +3359,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,6 +3368,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800628</v>
+        <v>130800760</v>
       </c>
       <c r="B28" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3505,39 +3505,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488274</v>
+        <v>488321</v>
       </c>
       <c r="R28" t="n">
-        <v>6721118</v>
+        <v>6721317</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3569,7 +3564,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3579,7 +3574,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3606,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800760</v>
+        <v>130800628</v>
       </c>
       <c r="B29" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3617,34 +3612,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488321</v>
+        <v>488274</v>
       </c>
       <c r="R29" t="n">
-        <v>6721317</v>
+        <v>6721118</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800761</v>
+        <v>130800762</v>
       </c>
       <c r="B30" t="n">
         <v>79243</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488353</v>
+        <v>488314</v>
       </c>
       <c r="R30" t="n">
-        <v>6721338</v>
+        <v>6721463</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,7 +3820,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800762</v>
+        <v>130800761</v>
       </c>
       <c r="B31" t="n">
         <v>79243</v>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488314</v>
+        <v>488353</v>
       </c>
       <c r="R31" t="n">
-        <v>6721463</v>
+        <v>6721338</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4467,7 +4467,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130800765</v>
+        <v>130800743</v>
       </c>
       <c r="B37" t="n">
         <v>79243</v>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488294</v>
+        <v>488261</v>
       </c>
       <c r="R37" t="n">
-        <v>6721432</v>
+        <v>6721212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4681,7 +4681,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130800743</v>
+        <v>130800765</v>
       </c>
       <c r="B39" t="n">
         <v>79243</v>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488261</v>
+        <v>488294</v>
       </c>
       <c r="R39" t="n">
-        <v>6721212</v>
+        <v>6721432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800738</v>
+        <v>130800753</v>
       </c>
       <c r="B43" t="n">
         <v>79243</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488241</v>
+        <v>488256</v>
       </c>
       <c r="R43" t="n">
-        <v>6721318</v>
+        <v>6721103</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800753</v>
+        <v>130800738</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488256</v>
+        <v>488241</v>
       </c>
       <c r="R44" t="n">
-        <v>6721103</v>
+        <v>6721318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800731</v>
+        <v>130800744</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488290</v>
+        <v>488254</v>
       </c>
       <c r="R45" t="n">
-        <v>6721380</v>
+        <v>6721200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800744</v>
+        <v>130800731</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488254</v>
+        <v>488290</v>
       </c>
       <c r="R46" t="n">
-        <v>6721200</v>
+        <v>6721380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130800737</v>
+        <v>130800748</v>
       </c>
       <c r="B2" t="n">
         <v>79243</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488255</v>
+        <v>488228</v>
       </c>
       <c r="R2" t="n">
-        <v>6721336</v>
+        <v>6721082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130800748</v>
+        <v>130800759</v>
       </c>
       <c r="B3" t="n">
         <v>79243</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488228</v>
+        <v>488315</v>
       </c>
       <c r="R3" t="n">
-        <v>6721082</v>
+        <v>6721292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130800759</v>
+        <v>130800737</v>
       </c>
       <c r="B4" t="n">
         <v>79243</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488315</v>
+        <v>488255</v>
       </c>
       <c r="R4" t="n">
-        <v>6721292</v>
+        <v>6721336</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130800747</v>
+        <v>130800767</v>
       </c>
       <c r="B10" t="n">
         <v>79243</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488252</v>
+        <v>488277</v>
       </c>
       <c r="R10" t="n">
-        <v>6721136</v>
+        <v>6721389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130800740</v>
+        <v>130800746</v>
       </c>
       <c r="B11" t="n">
         <v>79243</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488259</v>
+        <v>488260</v>
       </c>
       <c r="R11" t="n">
-        <v>6721276</v>
+        <v>6721168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130800767</v>
+        <v>130800747</v>
       </c>
       <c r="B12" t="n">
         <v>79243</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488277</v>
+        <v>488252</v>
       </c>
       <c r="R12" t="n">
-        <v>6721389</v>
+        <v>6721136</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130800746</v>
+        <v>130800740</v>
       </c>
       <c r="B13" t="n">
         <v>79243</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488260</v>
+        <v>488259</v>
       </c>
       <c r="R13" t="n">
-        <v>6721168</v>
+        <v>6721276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2291,50 +2291,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800615</v>
+        <v>130800750</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>79243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488401</v>
+        <v>488188</v>
       </c>
       <c r="R17" t="n">
-        <v>6721155</v>
+        <v>6721096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,7 +2361,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2376,7 +2371,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,7 +2398,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800750</v>
+        <v>130800745</v>
       </c>
       <c r="B18" t="n">
         <v>79243</v>
@@ -2438,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488188</v>
+        <v>488254</v>
       </c>
       <c r="R18" t="n">
-        <v>6721096</v>
+        <v>6721190</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,7 +2468,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2483,7 +2478,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2510,45 +2505,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800745</v>
+        <v>130800615</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>57073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488254</v>
+        <v>488401</v>
       </c>
       <c r="R19" t="n">
-        <v>6721190</v>
+        <v>6721155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,50 +2617,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130800770</v>
+        <v>130800752</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488368</v>
+        <v>488249</v>
       </c>
       <c r="R20" t="n">
-        <v>6721128</v>
+        <v>6721089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2702,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,45 +2724,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130800752</v>
+        <v>130800770</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488249</v>
+        <v>488368</v>
       </c>
       <c r="R21" t="n">
-        <v>6721089</v>
+        <v>6721128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,38 +3055,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130800625</v>
+        <v>130800640</v>
       </c>
       <c r="B24" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488400</v>
+        <v>488413</v>
       </c>
       <c r="R24" t="n">
-        <v>6721188</v>
+        <v>6721172</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,6 +3149,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3274,38 +3275,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800640</v>
+        <v>130800625</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3314,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488413</v>
+        <v>488400</v>
       </c>
       <c r="R26" t="n">
-        <v>6721172</v>
+        <v>6721188</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,7 +3350,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3360,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3369,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130800760</v>
+        <v>130800762</v>
       </c>
       <c r="B28" t="n">
         <v>79243</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488321</v>
+        <v>488314</v>
       </c>
       <c r="R28" t="n">
-        <v>6721317</v>
+        <v>6721463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130800628</v>
+        <v>130800760</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3612,39 +3612,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488274</v>
+        <v>488321</v>
       </c>
       <c r="R29" t="n">
-        <v>6721118</v>
+        <v>6721317</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3676,7 +3671,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3686,7 +3681,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,7 +3708,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130800762</v>
+        <v>130800761</v>
       </c>
       <c r="B30" t="n">
         <v>79243</v>
@@ -3748,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488314</v>
+        <v>488353</v>
       </c>
       <c r="R30" t="n">
-        <v>6721463</v>
+        <v>6721338</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,7 +3778,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3793,7 +3788,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,10 +3815,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130800761</v>
+        <v>130800628</v>
       </c>
       <c r="B31" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,34 +3826,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488353</v>
+        <v>488274</v>
       </c>
       <c r="R31" t="n">
-        <v>6721338</v>
+        <v>6721118</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,7 +3927,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130800742</v>
+        <v>130800757</v>
       </c>
       <c r="B32" t="n">
         <v>79243</v>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488259</v>
+        <v>488454</v>
       </c>
       <c r="R32" t="n">
-        <v>6721246</v>
+        <v>6721175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130800757</v>
+        <v>130800742</v>
       </c>
       <c r="B33" t="n">
         <v>79243</v>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488454</v>
+        <v>488259</v>
       </c>
       <c r="R33" t="n">
-        <v>6721175</v>
+        <v>6721246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4248,50 +4248,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R35" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4323,7 +4318,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4333,7 +4328,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,45 +4355,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R36" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800753</v>
+        <v>130800744</v>
       </c>
       <c r="B43" t="n">
         <v>79243</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488256</v>
+        <v>488254</v>
       </c>
       <c r="R43" t="n">
-        <v>6721103</v>
+        <v>6721200</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800738</v>
+        <v>130800731</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488241</v>
+        <v>488290</v>
       </c>
       <c r="R44" t="n">
-        <v>6721318</v>
+        <v>6721380</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800744</v>
+        <v>130800753</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488254</v>
+        <v>488256</v>
       </c>
       <c r="R45" t="n">
-        <v>6721200</v>
+        <v>6721103</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800731</v>
+        <v>130800738</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488290</v>
+        <v>488241</v>
       </c>
       <c r="R46" t="n">
-        <v>6721380</v>
+        <v>6721318</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130800759</v>
+        <v>130800737</v>
       </c>
       <c r="B3" t="n">
         <v>79243</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488315</v>
+        <v>488255</v>
       </c>
       <c r="R3" t="n">
-        <v>6721292</v>
+        <v>6721336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130800737</v>
+        <v>130800759</v>
       </c>
       <c r="B4" t="n">
         <v>79243</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488255</v>
+        <v>488315</v>
       </c>
       <c r="R4" t="n">
-        <v>6721336</v>
+        <v>6721292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800639</v>
+        <v>130800615</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>57073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,27 +2077,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488441</v>
+        <v>488401</v>
       </c>
       <c r="R15" t="n">
-        <v>6721177</v>
+        <v>6721155</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2160,7 +2160,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2505,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130800615</v>
+        <v>130800639</v>
       </c>
       <c r="B19" t="n">
-        <v>57073</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,27 +2515,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2545,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488401</v>
+        <v>488441</v>
       </c>
       <c r="R19" t="n">
-        <v>6721155</v>
+        <v>6721177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2590,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,6 +2598,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130800734</v>
+        <v>130800624</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,34 +2847,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488276</v>
+        <v>488277</v>
       </c>
       <c r="R22" t="n">
-        <v>6721374</v>
+        <v>6721389</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2911,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2916,7 +2921,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2943,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130800624</v>
+        <v>130800734</v>
       </c>
       <c r="B23" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2954,39 +2959,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488277</v>
+        <v>488276</v>
       </c>
       <c r="R23" t="n">
-        <v>6721389</v>
+        <v>6721374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4248,45 +4248,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R35" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4328,7 +4333,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,50 +4360,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R36" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 43222-2024 artfynd.xlsx
+++ b/artfynd/A 43222-2024 artfynd.xlsx
@@ -2066,50 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130800615</v>
+        <v>130800750</v>
       </c>
       <c r="B15" t="n">
-        <v>57073</v>
+        <v>79243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488401</v>
+        <v>488188</v>
       </c>
       <c r="R15" t="n">
-        <v>6721155</v>
+        <v>6721096</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,50 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130800769</v>
+        <v>130800745</v>
       </c>
       <c r="B16" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488274</v>
+        <v>488254</v>
       </c>
       <c r="R16" t="n">
-        <v>6721118</v>
+        <v>6721190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,45 +2280,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130800750</v>
+        <v>130800769</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488188</v>
+        <v>488274</v>
       </c>
       <c r="R17" t="n">
-        <v>6721096</v>
+        <v>6721118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,45 +2392,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130800745</v>
+        <v>130800615</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>57073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488254</v>
+        <v>488401</v>
       </c>
       <c r="R18" t="n">
-        <v>6721190</v>
+        <v>6721155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130800756</v>
+        <v>130800625</v>
       </c>
       <c r="B25" t="n">
-        <v>79243</v>
+        <v>57881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3179,34 +3179,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488470</v>
+        <v>488400</v>
       </c>
       <c r="R25" t="n">
-        <v>6721165</v>
+        <v>6721188</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3238,7 +3243,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3248,7 +3253,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,10 +3280,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130800625</v>
+        <v>130800756</v>
       </c>
       <c r="B26" t="n">
-        <v>57881</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3286,39 +3291,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488400</v>
+        <v>488470</v>
       </c>
       <c r="R26" t="n">
-        <v>6721188</v>
+        <v>6721165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4248,50 +4248,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130800771</v>
+        <v>130800758</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>79243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488277</v>
+        <v>488421</v>
       </c>
       <c r="R35" t="n">
-        <v>6721389</v>
+        <v>6721174</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4323,7 +4318,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4333,7 +4328,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,45 +4355,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130800758</v>
+        <v>130800771</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skinnaråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488421</v>
+        <v>488277</v>
       </c>
       <c r="R36" t="n">
-        <v>6721174</v>
+        <v>6721389</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5119,7 +5119,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130800744</v>
+        <v>130800753</v>
       </c>
       <c r="B43" t="n">
         <v>79243</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488254</v>
+        <v>488256</v>
       </c>
       <c r="R43" t="n">
-        <v>6721200</v>
+        <v>6721103</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130800731</v>
+        <v>130800738</v>
       </c>
       <c r="B44" t="n">
         <v>79243</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488290</v>
+        <v>488241</v>
       </c>
       <c r="R44" t="n">
-        <v>6721380</v>
+        <v>6721318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130800753</v>
+        <v>130800744</v>
       </c>
       <c r="B45" t="n">
         <v>79243</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488256</v>
+        <v>488254</v>
       </c>
       <c r="R45" t="n">
-        <v>6721103</v>
+        <v>6721200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5440,7 +5440,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130800738</v>
+        <v>130800731</v>
       </c>
       <c r="B46" t="n">
         <v>79243</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488241</v>
+        <v>488290</v>
       </c>
       <c r="R46" t="n">
-        <v>6721318</v>
+        <v>6721380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
